--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,6 +890,2840 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128941893</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>476608</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6848604</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128940813</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476011</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6848344</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128940298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79152</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476045</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6848362</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128938430</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476242</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6848360</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128940090</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6848366</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128938254</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>476311</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6848373</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128937356</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97503</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>476538</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6848401</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128939797</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>476165</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6848345</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128940061</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476098</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6848356</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128938038</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476366</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6848335</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128940838</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>476019</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6848346</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128938294</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>476273</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6848367</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128940807</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97509</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>476017</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6848311</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128941680</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>476579</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6848505</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128939810</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79152</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>185</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>476160</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6848351</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128938486</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>476227</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6848338</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128939377</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79152</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>476172</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6848367</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128939975</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79152</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>185</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>476095</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6848329</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128939967</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>476108</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6848326</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128940964</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>476162</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6848440</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128940754</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>475993</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6848330</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128940018</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>476093</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6848323</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128938481</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>476239</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6848323</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128940871</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>476032</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6848339</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128941699</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>476591</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6848497</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128941818</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>476588</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6848599</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128938096</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>476310</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6848364</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Små plantor i tidig fas.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128941972</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>476631</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6848589</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128940090</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,32 +1501,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128937356</v>
+        <v>128938038</v>
       </c>
       <c r="B10" t="n">
-        <v>97503</v>
+        <v>57880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476538</v>
+        <v>476366</v>
       </c>
       <c r="R10" t="n">
-        <v>6848401</v>
+        <v>6848335</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>128939797</v>
       </c>
       <c r="B11" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>128940061</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,32 +1806,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128938038</v>
+        <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>97507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476366</v>
+        <v>476538</v>
       </c>
       <c r="R13" t="n">
-        <v>6848335</v>
+        <v>6848401</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128940838</v>
+        <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,26 +1931,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476019</v>
+        <v>476273</v>
       </c>
       <c r="R14" t="n">
-        <v>6848346</v>
+        <v>6848367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,10 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128938294</v>
+        <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,17 +2028,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476273</v>
+        <v>476019</v>
       </c>
       <c r="R15" t="n">
-        <v>6848367</v>
+        <v>6848346</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,54 +2203,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128941680</v>
+        <v>128939810</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>79156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476579</v>
+        <v>476160</v>
       </c>
       <c r="R17" t="n">
-        <v>6848505</v>
+        <v>6848351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,45 +2300,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128939810</v>
+        <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>79152</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476160</v>
+        <v>476227</v>
       </c>
       <c r="R18" t="n">
-        <v>6848351</v>
+        <v>6848338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,22 +2394,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128938486</v>
+        <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476227</v>
+        <v>476579</v>
       </c>
       <c r="R19" t="n">
-        <v>6848338</v>
+        <v>6848505</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,22 +2500,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939377</v>
+        <v>128939975</v>
       </c>
       <c r="B20" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476172</v>
+        <v>476095</v>
       </c>
       <c r="R20" t="n">
-        <v>6848367</v>
+        <v>6848329</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939975</v>
+        <v>128939377</v>
       </c>
       <c r="B21" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476095</v>
+        <v>476172</v>
       </c>
       <c r="R21" t="n">
-        <v>6848329</v>
+        <v>6848367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>128940964</v>
       </c>
       <c r="B23" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128940754</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>128938481</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,32 +1501,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128938038</v>
+        <v>128937356</v>
       </c>
       <c r="B10" t="n">
-        <v>57880</v>
+        <v>97507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476366</v>
+        <v>476538</v>
       </c>
       <c r="R10" t="n">
-        <v>6848335</v>
+        <v>6848401</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,54 +1700,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128940061</v>
+        <v>128938038</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>57880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476098</v>
+        <v>476366</v>
       </c>
       <c r="R12" t="n">
-        <v>6848356</v>
+        <v>6848335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,60 +1785,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128937356</v>
+        <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>97507</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476538</v>
+        <v>476098</v>
       </c>
       <c r="R13" t="n">
-        <v>6848401</v>
+        <v>6848356</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2512,32 +2512,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939975</v>
+        <v>128939967</v>
       </c>
       <c r="B20" t="n">
-        <v>79156</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476095</v>
+        <v>476108</v>
       </c>
       <c r="R20" t="n">
-        <v>6848329</v>
+        <v>6848326</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,12 +2597,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939967</v>
+        <v>128939975</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>79156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476108</v>
+        <v>476095</v>
       </c>
       <c r="R22" t="n">
-        <v>6848326</v>
+        <v>6848329</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128940754</v>
+        <v>128938481</v>
       </c>
       <c r="B24" t="n">
         <v>98636</v>
@@ -2928,17 +2928,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475993</v>
+        <v>476239</v>
       </c>
       <c r="R24" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,7 +3112,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128938481</v>
+        <v>128940754</v>
       </c>
       <c r="B26" t="n">
         <v>98636</v>
@@ -3131,26 +3140,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476239</v>
+        <v>475993</v>
       </c>
       <c r="R26" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,32 +1501,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128937356</v>
+        <v>128938038</v>
       </c>
       <c r="B10" t="n">
-        <v>97507</v>
+        <v>57880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476538</v>
+        <v>476366</v>
       </c>
       <c r="R10" t="n">
-        <v>6848401</v>
+        <v>6848335</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,32 +1700,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128938038</v>
+        <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>57880</v>
+        <v>97507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476366</v>
+        <v>476538</v>
       </c>
       <c r="R12" t="n">
-        <v>6848335</v>
+        <v>6848401</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2512,32 +2512,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939967</v>
+        <v>128939377</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>79156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476108</v>
+        <v>476172</v>
       </c>
       <c r="R20" t="n">
-        <v>6848326</v>
+        <v>6848367</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,19 +2597,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939377</v>
+        <v>128939975</v>
       </c>
       <c r="B21" t="n">
         <v>79156</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476172</v>
+        <v>476095</v>
       </c>
       <c r="R21" t="n">
-        <v>6848367</v>
+        <v>6848329</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939975</v>
+        <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>79156</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476095</v>
+        <v>476108</v>
       </c>
       <c r="R22" t="n">
-        <v>6848329</v>
+        <v>6848326</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128940090</v>
       </c>
       <c r="B8" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,45 +1501,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128938038</v>
+        <v>128940061</v>
       </c>
       <c r="B10" t="n">
-        <v>57880</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476366</v>
+        <v>476098</v>
       </c>
       <c r="R10" t="n">
-        <v>6848335</v>
+        <v>6848356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1595,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1601,7 +1610,7 @@
         <v>128939797</v>
       </c>
       <c r="B11" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,32 +1709,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128937356</v>
+        <v>128938038</v>
       </c>
       <c r="B12" t="n">
-        <v>97507</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476538</v>
+        <v>476366</v>
       </c>
       <c r="R12" t="n">
-        <v>6848401</v>
+        <v>6848335</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,57 +1806,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128940061</v>
+        <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>97514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476098</v>
+        <v>476538</v>
       </c>
       <c r="R13" t="n">
-        <v>6848356</v>
+        <v>6848401</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,45 +2203,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128939810</v>
+        <v>128938486</v>
       </c>
       <c r="B17" t="n">
-        <v>79156</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476160</v>
+        <v>476227</v>
       </c>
       <c r="R17" t="n">
-        <v>6848351</v>
+        <v>6848338</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,22 +2297,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128938486</v>
+        <v>128941680</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,7 +2339,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2344,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476227</v>
+        <v>476579</v>
       </c>
       <c r="R18" t="n">
-        <v>6848338</v>
+        <v>6848505</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,66 +2403,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941680</v>
+        <v>128939810</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>79061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476579</v>
+        <v>476160</v>
       </c>
       <c r="R19" t="n">
-        <v>6848505</v>
+        <v>6848351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
         <v>128939377</v>
       </c>
       <c r="B20" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>128939975</v>
       </c>
       <c r="B21" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>128940964</v>
       </c>
       <c r="B23" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,48 +1501,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128939797</v>
+        <v>128937356</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>97522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476165</v>
+        <v>476538</v>
       </c>
       <c r="R10" t="n">
-        <v>6848345</v>
+        <v>6848401</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,19 +1586,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128938038</v>
+        <v>128939797</v>
       </c>
       <c r="B11" t="n">
         <v>57883</v>
@@ -1634,14 +1629,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476366</v>
+        <v>476165</v>
       </c>
       <c r="R11" t="n">
-        <v>6848335</v>
+        <v>6848345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,6 +1671,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,66 +1688,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128940061</v>
+        <v>128938038</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476098</v>
+        <v>476366</v>
       </c>
       <c r="R12" t="n">
-        <v>6848356</v>
+        <v>6848335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,60 +1785,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128937356</v>
+        <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>97522</v>
+        <v>98651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476538</v>
+        <v>476098</v>
       </c>
       <c r="R13" t="n">
-        <v>6848401</v>
+        <v>6848356</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,48 +1501,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128937356</v>
+        <v>128939797</v>
       </c>
       <c r="B10" t="n">
-        <v>97522</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476538</v>
+        <v>476165</v>
       </c>
       <c r="R10" t="n">
-        <v>6848401</v>
+        <v>6848345</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,19 +1591,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B11" t="n">
         <v>57883</v>
@@ -1629,14 +1634,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R11" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,11 +1676,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,44 +1688,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128938038</v>
+        <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>97527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476366</v>
+        <v>476538</v>
       </c>
       <c r="R12" t="n">
-        <v>6848335</v>
+        <v>6848401</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128940871</v>
+        <v>128941699</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,29 +3237,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476032</v>
+        <v>476591</v>
       </c>
       <c r="R27" t="n">
-        <v>6848339</v>
+        <v>6848497</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3303,22 +3294,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128941699</v>
+        <v>128940871</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3343,20 +3334,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476591</v>
+        <v>476032</v>
       </c>
       <c r="R28" t="n">
-        <v>6848497</v>
+        <v>6848339</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3400,12 +3400,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128940090</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B10" t="n">
         <v>57883</v>
@@ -1532,14 +1532,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R10" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,11 +1574,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1591,44 +1586,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128938038</v>
+        <v>128937356</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>97530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476366</v>
+        <v>476538</v>
       </c>
       <c r="R11" t="n">
-        <v>6848335</v>
+        <v>6848401</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,48 +1695,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128937356</v>
+        <v>128939797</v>
       </c>
       <c r="B12" t="n">
-        <v>97527</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476538</v>
+        <v>476165</v>
       </c>
       <c r="R12" t="n">
-        <v>6848401</v>
+        <v>6848345</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,6 +1766,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,12 +1785,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
         <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128939810</v>
       </c>
       <c r="B17" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>128939377</v>
       </c>
       <c r="B20" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>128939975</v>
       </c>
       <c r="B21" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>128940964</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128941699</v>
+        <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,20 +3237,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476591</v>
+        <v>476032</v>
       </c>
       <c r="R27" t="n">
-        <v>6848497</v>
+        <v>6848339</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3294,22 +3303,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128940871</v>
+        <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3334,29 +3343,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476032</v>
+        <v>476591</v>
       </c>
       <c r="R28" t="n">
-        <v>6848339</v>
+        <v>6848497</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3400,12 +3400,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,45 +1501,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128938038</v>
+        <v>128940061</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476366</v>
+        <v>476098</v>
       </c>
       <c r="R10" t="n">
-        <v>6848335</v>
+        <v>6848356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,60 +1595,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128937356</v>
+        <v>128939797</v>
       </c>
       <c r="B11" t="n">
-        <v>97530</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476538</v>
+        <v>476165</v>
       </c>
       <c r="R11" t="n">
-        <v>6848401</v>
+        <v>6848345</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,6 +1678,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,19 +1697,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B12" t="n">
         <v>57883</v>
@@ -1726,14 +1740,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R12" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,11 +1782,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1785,69 +1794,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128940061</v>
+        <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476098</v>
+        <v>476538</v>
       </c>
       <c r="R13" t="n">
-        <v>6848356</v>
+        <v>6848401</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,54 +1501,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128940061</v>
+        <v>128939797</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476098</v>
+        <v>476165</v>
       </c>
       <c r="R10" t="n">
-        <v>6848356</v>
+        <v>6848345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B11" t="n">
         <v>57883</v>
@@ -1638,14 +1634,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R11" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,11 +1676,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1697,44 +1688,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128938038</v>
+        <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>97530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476366</v>
+        <v>476538</v>
       </c>
       <c r="R12" t="n">
-        <v>6848335</v>
+        <v>6848401</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,48 +1797,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128937356</v>
+        <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476538</v>
+        <v>476098</v>
       </c>
       <c r="R13" t="n">
-        <v>6848401</v>
+        <v>6848356</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,45 +1501,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128939797</v>
+        <v>128940061</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476165</v>
+        <v>476098</v>
       </c>
       <c r="R10" t="n">
-        <v>6848345</v>
+        <v>6848356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1581,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,7 +1607,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128938038</v>
+        <v>128939797</v>
       </c>
       <c r="B11" t="n">
         <v>57883</v>
@@ -1634,14 +1638,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476366</v>
+        <v>476165</v>
       </c>
       <c r="R11" t="n">
-        <v>6848335</v>
+        <v>6848345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,6 +1680,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,44 +1697,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128937356</v>
+        <v>128938038</v>
       </c>
       <c r="B12" t="n">
-        <v>97530</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476538</v>
+        <v>476366</v>
       </c>
       <c r="R12" t="n">
-        <v>6848401</v>
+        <v>6848335</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,57 +1806,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128940061</v>
+        <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476098</v>
+        <v>476538</v>
       </c>
       <c r="R13" t="n">
-        <v>6848356</v>
+        <v>6848401</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2203,45 +2203,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128939810</v>
+        <v>128941680</v>
       </c>
       <c r="B17" t="n">
-        <v>79067</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476160</v>
+        <v>476579</v>
       </c>
       <c r="R17" t="n">
-        <v>6848351</v>
+        <v>6848505</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,54 +2309,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128938486</v>
+        <v>128939810</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>79067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476227</v>
+        <v>476160</v>
       </c>
       <c r="R18" t="n">
-        <v>6848338</v>
+        <v>6848351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,19 +2394,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941680</v>
+        <v>128938486</v>
       </c>
       <c r="B19" t="n">
         <v>98659</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476579</v>
+        <v>476227</v>
       </c>
       <c r="R19" t="n">
-        <v>6848505</v>
+        <v>6848338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,12 +2500,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128940090</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>128940061</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128939797</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128938038</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,54 +2203,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128941680</v>
+        <v>128939810</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>79071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476579</v>
+        <v>476160</v>
       </c>
       <c r="R17" t="n">
-        <v>6848505</v>
+        <v>6848351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,45 +2300,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128939810</v>
+        <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>79067</v>
+        <v>98669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476160</v>
+        <v>476227</v>
       </c>
       <c r="R18" t="n">
-        <v>6848351</v>
+        <v>6848338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,22 +2394,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128938486</v>
+        <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476227</v>
+        <v>476579</v>
       </c>
       <c r="R19" t="n">
-        <v>6848338</v>
+        <v>6848505</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,44 +2500,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939377</v>
+        <v>128939967</v>
       </c>
       <c r="B20" t="n">
-        <v>79067</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476172</v>
+        <v>476108</v>
       </c>
       <c r="R20" t="n">
-        <v>6848367</v>
+        <v>6848326</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,22 +2597,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939975</v>
+        <v>128939377</v>
       </c>
       <c r="B21" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476095</v>
+        <v>476172</v>
       </c>
       <c r="R21" t="n">
-        <v>6848329</v>
+        <v>6848367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939967</v>
+        <v>128939975</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>79071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476108</v>
+        <v>476095</v>
       </c>
       <c r="R22" t="n">
-        <v>6848326</v>
+        <v>6848329</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
         <v>128940964</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128940018</v>
+        <v>128940754</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,26 +3034,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476093</v>
+        <v>475993</v>
       </c>
       <c r="R25" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128940754</v>
+        <v>128940018</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,17 +3131,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475993</v>
+        <v>476093</v>
       </c>
       <c r="R26" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,54 +1501,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128940061</v>
+        <v>128939797</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476098</v>
+        <v>476165</v>
       </c>
       <c r="R10" t="n">
-        <v>6848356</v>
+        <v>6848345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B11" t="n">
         <v>57885</v>
@@ -1638,14 +1634,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R11" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,11 +1676,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1697,57 +1688,66 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128938038</v>
+        <v>128940061</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476366</v>
+        <v>476098</v>
       </c>
       <c r="R12" t="n">
-        <v>6848335</v>
+        <v>6848356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,12 +1794,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,57 +1700,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128940061</v>
+        <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>97547</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476098</v>
+        <v>476538</v>
       </c>
       <c r="R12" t="n">
-        <v>6848356</v>
+        <v>6848401</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,60 +1785,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128937356</v>
+        <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>97540</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476538</v>
+        <v>476098</v>
       </c>
       <c r="R13" t="n">
-        <v>6848401</v>
+        <v>6848356</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128938486</v>
+        <v>128941680</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476227</v>
+        <v>476579</v>
       </c>
       <c r="R18" t="n">
-        <v>6848338</v>
+        <v>6848505</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,22 +2394,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941680</v>
+        <v>128938486</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476579</v>
+        <v>476227</v>
       </c>
       <c r="R19" t="n">
-        <v>6848505</v>
+        <v>6848338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,44 +2500,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939967</v>
+        <v>128939975</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>79071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476108</v>
+        <v>476095</v>
       </c>
       <c r="R20" t="n">
-        <v>6848326</v>
+        <v>6848329</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,12 +2597,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939975</v>
+        <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>79071</v>
+        <v>98676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476095</v>
+        <v>476108</v>
       </c>
       <c r="R22" t="n">
-        <v>6848329</v>
+        <v>6848326</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128938481</v>
+        <v>128940754</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,26 +2928,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476239</v>
+        <v>475993</v>
       </c>
       <c r="R24" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,10 +2997,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128940754</v>
+        <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,17 +3025,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475993</v>
+        <v>476093</v>
       </c>
       <c r="R25" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128940018</v>
+        <v>128938481</v>
       </c>
       <c r="B26" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476093</v>
+        <v>476239</v>
       </c>
       <c r="R26" t="n">
         <v>6848323</v>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128940090</v>
       </c>
       <c r="B8" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,14 +1532,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R10" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,11 +1574,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1591,57 +1586,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128938038</v>
+        <v>128940061</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476366</v>
+        <v>476098</v>
       </c>
       <c r="R11" t="n">
-        <v>6848335</v>
+        <v>6848356</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1692,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1703,7 +1707,7 @@
         <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,54 +1801,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128940061</v>
+        <v>128939797</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476098</v>
+        <v>476165</v>
       </c>
       <c r="R13" t="n">
-        <v>6848356</v>
+        <v>6848345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,6 +1872,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128939810</v>
       </c>
       <c r="B17" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128941680</v>
+        <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476579</v>
+        <v>476227</v>
       </c>
       <c r="R18" t="n">
-        <v>6848505</v>
+        <v>6848338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,22 +2394,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128938486</v>
+        <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476227</v>
+        <v>476579</v>
       </c>
       <c r="R19" t="n">
-        <v>6848338</v>
+        <v>6848505</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,44 +2500,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939975</v>
+        <v>128939967</v>
       </c>
       <c r="B20" t="n">
-        <v>79071</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476095</v>
+        <v>476108</v>
       </c>
       <c r="R20" t="n">
-        <v>6848329</v>
+        <v>6848326</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,12 +2597,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2612,7 +2612,7 @@
         <v>128939377</v>
       </c>
       <c r="B21" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939967</v>
+        <v>128939975</v>
       </c>
       <c r="B22" t="n">
-        <v>98676</v>
+        <v>79073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476108</v>
+        <v>476095</v>
       </c>
       <c r="R22" t="n">
-        <v>6848326</v>
+        <v>6848329</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
         <v>128940964</v>
       </c>
       <c r="B23" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128940754</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>128938481</v>
       </c>
       <c r="B26" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128938038</v>
+        <v>128939797</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1532,14 +1532,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476366</v>
+        <v>476165</v>
       </c>
       <c r="R10" t="n">
-        <v>6848335</v>
+        <v>6848345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,6 +1574,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1586,66 +1591,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128940061</v>
+        <v>128938038</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476098</v>
+        <v>476366</v>
       </c>
       <c r="R11" t="n">
-        <v>6848356</v>
+        <v>6848335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,60 +1688,69 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128937356</v>
+        <v>128940061</v>
       </c>
       <c r="B12" t="n">
-        <v>97549</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476538</v>
+        <v>476098</v>
       </c>
       <c r="R12" t="n">
-        <v>6848401</v>
+        <v>6848356</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1789,60 +1794,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128939797</v>
+        <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>97549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476165</v>
+        <v>476538</v>
       </c>
       <c r="R13" t="n">
-        <v>6848345</v>
+        <v>6848401</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1872,11 +1877,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2203,45 +2203,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128939810</v>
+        <v>128941680</v>
       </c>
       <c r="B17" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476160</v>
+        <v>476579</v>
       </c>
       <c r="R17" t="n">
-        <v>6848351</v>
+        <v>6848505</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,54 +2415,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941680</v>
+        <v>128939810</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476579</v>
+        <v>476160</v>
       </c>
       <c r="R19" t="n">
-        <v>6848505</v>
+        <v>6848351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,32 +2512,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939967</v>
+        <v>128939377</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476108</v>
+        <v>476172</v>
       </c>
       <c r="R20" t="n">
-        <v>6848326</v>
+        <v>6848367</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,19 +2597,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939377</v>
+        <v>128939975</v>
       </c>
       <c r="B21" t="n">
         <v>79073</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476172</v>
+        <v>476095</v>
       </c>
       <c r="R21" t="n">
-        <v>6848367</v>
+        <v>6848329</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939975</v>
+        <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476095</v>
+        <v>476108</v>
       </c>
       <c r="R22" t="n">
-        <v>6848329</v>
+        <v>6848326</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128940754</v>
+        <v>128938481</v>
       </c>
       <c r="B24" t="n">
         <v>98678</v>
@@ -2928,17 +2928,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475993</v>
+        <v>476239</v>
       </c>
       <c r="R24" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,7 +3112,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128938481</v>
+        <v>128940754</v>
       </c>
       <c r="B26" t="n">
         <v>98678</v>
@@ -3131,26 +3140,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476239</v>
+        <v>475993</v>
       </c>
       <c r="R26" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -1104,48 +1104,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128940298</v>
+        <v>128938430</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476045</v>
+        <v>476242</v>
       </c>
       <c r="R6" t="n">
-        <v>6848362</v>
+        <v>6848360</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,69 +1198,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128938430</v>
+        <v>128940298</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476242</v>
+        <v>476045</v>
       </c>
       <c r="R7" t="n">
-        <v>6848360</v>
+        <v>6848362</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128938430</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,45 +1501,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128939797</v>
+        <v>128940061</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476165</v>
+        <v>476098</v>
       </c>
       <c r="R10" t="n">
-        <v>6848345</v>
+        <v>6848356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1581,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,32 +1607,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128938038</v>
+        <v>128937356</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>97575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476366</v>
+        <v>476538</v>
       </c>
       <c r="R11" t="n">
-        <v>6848335</v>
+        <v>6848401</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,54 +1704,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128940061</v>
+        <v>128939797</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476098</v>
+        <v>476165</v>
       </c>
       <c r="R12" t="n">
-        <v>6848356</v>
+        <v>6848345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,6 +1775,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,32 +1806,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128937356</v>
+        <v>128938038</v>
       </c>
       <c r="B13" t="n">
-        <v>97549</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476538</v>
+        <v>476366</v>
       </c>
       <c r="R13" t="n">
-        <v>6848401</v>
+        <v>6848335</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,54 +2203,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128941680</v>
+        <v>128939810</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476579</v>
+        <v>476160</v>
       </c>
       <c r="R17" t="n">
-        <v>6848505</v>
+        <v>6848351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128938486</v>
+        <v>128941680</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,7 +2330,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2353,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476227</v>
+        <v>476579</v>
       </c>
       <c r="R18" t="n">
-        <v>6848338</v>
+        <v>6848505</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,57 +2394,66 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128939810</v>
+        <v>128938486</v>
       </c>
       <c r="B19" t="n">
-        <v>79073</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476160</v>
+        <v>476227</v>
       </c>
       <c r="R19" t="n">
-        <v>6848351</v>
+        <v>6848338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,12 +2500,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128938481</v>
+        <v>128940754</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,26 +2928,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476239</v>
+        <v>475993</v>
       </c>
       <c r="R24" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,7 +3000,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128940754</v>
+        <v>128938481</v>
       </c>
       <c r="B26" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,17 +3131,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475993</v>
+        <v>476239</v>
       </c>
       <c r="R26" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,57 +1104,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128938430</v>
+        <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476242</v>
+        <v>476045</v>
       </c>
       <c r="R6" t="n">
-        <v>6848360</v>
+        <v>6848362</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,60 +1189,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128940298</v>
+        <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476045</v>
+        <v>476242</v>
       </c>
       <c r="R7" t="n">
-        <v>6848362</v>
+        <v>6848360</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,54 +1501,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128940061</v>
+        <v>128938038</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476098</v>
+        <v>476366</v>
       </c>
       <c r="R10" t="n">
-        <v>6848356</v>
+        <v>6848335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,60 +1586,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128937356</v>
+        <v>128939797</v>
       </c>
       <c r="B11" t="n">
-        <v>97575</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476538</v>
+        <v>476165</v>
       </c>
       <c r="R11" t="n">
-        <v>6848401</v>
+        <v>6848345</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1678,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,60 +1688,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128939797</v>
+        <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>97576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476165</v>
+        <v>476538</v>
       </c>
       <c r="R12" t="n">
-        <v>6848345</v>
+        <v>6848401</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1775,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,57 +1785,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128938038</v>
+        <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476366</v>
+        <v>476098</v>
       </c>
       <c r="R13" t="n">
-        <v>6848335</v>
+        <v>6848356</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,45 +2203,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128939810</v>
+        <v>128938486</v>
       </c>
       <c r="B17" t="n">
-        <v>79073</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476160</v>
+        <v>476227</v>
       </c>
       <c r="R17" t="n">
-        <v>6848351</v>
+        <v>6848338</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,12 +2297,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2303,7 +2312,7 @@
         <v>128941680</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,54 +2415,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128938486</v>
+        <v>128939810</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>79073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476227</v>
+        <v>476160</v>
       </c>
       <c r="R19" t="n">
-        <v>6848338</v>
+        <v>6848351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,12 +2500,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128940754</v>
+        <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,17 +2928,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475993</v>
+        <v>476239</v>
       </c>
       <c r="R24" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3103,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128938481</v>
+        <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,26 +3140,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476239</v>
+        <v>475993</v>
       </c>
       <c r="R26" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128938038</v>
+        <v>128939797</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1532,14 +1532,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476366</v>
+        <v>476165</v>
       </c>
       <c r="R10" t="n">
-        <v>6848335</v>
+        <v>6848345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,6 +1574,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1586,19 +1591,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1629,14 +1634,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R11" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,11 +1676,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,12 +1688,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
         <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128938486</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128941680</v>
       </c>
       <c r="B18" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128940090</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,48 +1501,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128939797</v>
+        <v>128937356</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>97581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476165</v>
+        <v>476538</v>
       </c>
       <c r="R10" t="n">
-        <v>6848345</v>
+        <v>6848401</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,19 +1586,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128938038</v>
+        <v>128939797</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1634,14 +1629,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476366</v>
+        <v>476165</v>
       </c>
       <c r="R11" t="n">
-        <v>6848335</v>
+        <v>6848345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,6 +1671,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,44 +1688,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128937356</v>
+        <v>128938038</v>
       </c>
       <c r="B12" t="n">
-        <v>97577</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476538</v>
+        <v>476366</v>
       </c>
       <c r="R12" t="n">
-        <v>6848401</v>
+        <v>6848335</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,54 +2203,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128938486</v>
+        <v>128939810</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476227</v>
+        <v>476160</v>
       </c>
       <c r="R17" t="n">
-        <v>6848338</v>
+        <v>6848351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2297,12 +2288,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2312,7 +2303,7 @@
         <v>128941680</v>
       </c>
       <c r="B18" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,45 +2406,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128939810</v>
+        <v>128938486</v>
       </c>
       <c r="B19" t="n">
-        <v>79073</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476160</v>
+        <v>476227</v>
       </c>
       <c r="R19" t="n">
-        <v>6848351</v>
+        <v>6848338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,12 +2500,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
         <v>128939377</v>
       </c>
       <c r="B20" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>128939975</v>
       </c>
       <c r="B21" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>128940964</v>
       </c>
       <c r="B23" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128938481</v>
+        <v>128940754</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,26 +2928,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476239</v>
+        <v>475993</v>
       </c>
       <c r="R24" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,7 +3000,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128940754</v>
+        <v>128938481</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,17 +3131,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475993</v>
+        <v>476239</v>
       </c>
       <c r="R26" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128940298</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128940090</v>
       </c>
       <c r="B8" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,48 +1501,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128937356</v>
+        <v>128939797</v>
       </c>
       <c r="B10" t="n">
-        <v>97581</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476538</v>
+        <v>476165</v>
       </c>
       <c r="R10" t="n">
-        <v>6848401</v>
+        <v>6848345</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,19 +1591,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128939797</v>
+        <v>128938038</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1629,14 +1634,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476165</v>
+        <v>476366</v>
       </c>
       <c r="R11" t="n">
-        <v>6848345</v>
+        <v>6848335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,11 +1676,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,57 +1688,66 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128938038</v>
+        <v>128940061</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476366</v>
+        <v>476098</v>
       </c>
       <c r="R12" t="n">
-        <v>6848335</v>
+        <v>6848356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,69 +1794,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128940061</v>
+        <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476098</v>
+        <v>476538</v>
       </c>
       <c r="R13" t="n">
-        <v>6848356</v>
+        <v>6848401</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128939810</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128941680</v>
+        <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476579</v>
+        <v>476227</v>
       </c>
       <c r="R18" t="n">
-        <v>6848505</v>
+        <v>6848338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,22 +2394,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128938486</v>
+        <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476227</v>
+        <v>476579</v>
       </c>
       <c r="R19" t="n">
-        <v>6848338</v>
+        <v>6848505</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,44 +2500,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939377</v>
+        <v>128939967</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476172</v>
+        <v>476108</v>
       </c>
       <c r="R20" t="n">
-        <v>6848367</v>
+        <v>6848326</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,22 +2597,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939975</v>
+        <v>128939377</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476095</v>
+        <v>476172</v>
       </c>
       <c r="R21" t="n">
-        <v>6848329</v>
+        <v>6848367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939967</v>
+        <v>128939975</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476108</v>
+        <v>476095</v>
       </c>
       <c r="R22" t="n">
-        <v>6848326</v>
+        <v>6848329</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
         <v>128940964</v>
       </c>
       <c r="B23" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128940754</v>
+        <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,17 +2928,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475993</v>
+        <v>476239</v>
       </c>
       <c r="R24" t="n">
-        <v>6848330</v>
+        <v>6848323</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3103,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128938481</v>
+        <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,26 +3140,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476239</v>
+        <v>475993</v>
       </c>
       <c r="R26" t="n">
-        <v>6848323</v>
+        <v>6848330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,57 +1700,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128940061</v>
+        <v>128937356</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>97587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476098</v>
+        <v>476538</v>
       </c>
       <c r="R12" t="n">
-        <v>6848356</v>
+        <v>6848401</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,60 +1785,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128937356</v>
+        <v>128940061</v>
       </c>
       <c r="B13" t="n">
-        <v>97583</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476538</v>
+        <v>476098</v>
       </c>
       <c r="R13" t="n">
-        <v>6848401</v>
+        <v>6848356</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,32 +2512,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939967</v>
+        <v>128939377</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476108</v>
+        <v>476172</v>
       </c>
       <c r="R20" t="n">
-        <v>6848326</v>
+        <v>6848367</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,19 +2597,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939377</v>
+        <v>128939975</v>
       </c>
       <c r="B21" t="n">
         <v>79076</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476172</v>
+        <v>476095</v>
       </c>
       <c r="R21" t="n">
-        <v>6848367</v>
+        <v>6848329</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939975</v>
+        <v>128939967</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476095</v>
+        <v>476108</v>
       </c>
       <c r="R22" t="n">
-        <v>6848329</v>
+        <v>6848326</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
         <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128941893</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128940813</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>128938430</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128938254</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,48 +1700,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128937356</v>
+        <v>128940061</v>
       </c>
       <c r="B12" t="n">
-        <v>97587</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476538</v>
+        <v>476098</v>
       </c>
       <c r="R12" t="n">
-        <v>6848401</v>
+        <v>6848356</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,69 +1794,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128940061</v>
+        <v>128937356</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>97595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476098</v>
+        <v>476538</v>
       </c>
       <c r="R13" t="n">
-        <v>6848356</v>
+        <v>6848401</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>128938294</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>128940838</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>128940807</v>
       </c>
       <c r="B16" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128941680</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,32 +2512,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939377</v>
+        <v>128939967</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476172</v>
+        <v>476108</v>
       </c>
       <c r="R20" t="n">
-        <v>6848367</v>
+        <v>6848326</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,19 +2597,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939975</v>
+        <v>128939377</v>
       </c>
       <c r="B21" t="n">
         <v>79076</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476095</v>
+        <v>476172</v>
       </c>
       <c r="R21" t="n">
-        <v>6848329</v>
+        <v>6848367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939967</v>
+        <v>128939975</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476108</v>
+        <v>476095</v>
       </c>
       <c r="R22" t="n">
-        <v>6848326</v>
+        <v>6848329</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
         <v>128938481</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>128940018</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128940754</v>
       </c>
       <c r="B26" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128940871</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128941699</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128941818</v>
       </c>
       <c r="B29" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>128938096</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128941972</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124080304</v>
+        <v>128939377</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476639</v>
+        <v>476172</v>
       </c>
       <c r="R2" t="n">
-        <v>6848564</v>
+        <v>6848367</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,64 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825368</v>
+        <v>128939810</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476114</v>
+        <v>476160</v>
       </c>
       <c r="R3" t="n">
-        <v>6848307</v>
+        <v>6848351</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,69 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128941893</v>
+        <v>128939975</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476608</v>
+        <v>476095</v>
       </c>
       <c r="R4" t="n">
-        <v>6848604</v>
+        <v>6848329</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128940813</v>
+        <v>128940298</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476011</v>
+        <v>476045</v>
       </c>
       <c r="R5" t="n">
-        <v>6848344</v>
+        <v>6848362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128940298</v>
+        <v>128940090</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476045</v>
+        <v>476102</v>
       </c>
       <c r="R6" t="n">
-        <v>6848362</v>
+        <v>6848366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,57 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128938430</v>
+        <v>128940964</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476242</v>
+        <v>476162</v>
       </c>
       <c r="R7" t="n">
-        <v>6848360</v>
+        <v>6848440</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128940090</v>
+        <v>128938038</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476102</v>
+        <v>476366</v>
       </c>
       <c r="R8" t="n">
-        <v>6848366</v>
+        <v>6848335</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128938254</v>
+        <v>128939797</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476311</v>
+        <v>476165</v>
       </c>
       <c r="R9" t="n">
-        <v>6848373</v>
+        <v>6848345</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,45 +1456,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128939797</v>
+        <v>124080304</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476165</v>
+        <v>476639</v>
       </c>
       <c r="R10" t="n">
-        <v>6848345</v>
+        <v>6848564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,17 +1530,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,60 +1550,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128938038</v>
+        <v>124825368</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476366</v>
+        <v>476114</v>
       </c>
       <c r="R11" t="n">
-        <v>6848335</v>
+        <v>6848307</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,12 +1631,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,22 +1656,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128940061</v>
+        <v>124825371</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,27 +1698,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476098</v>
+        <v>476053</v>
       </c>
       <c r="R12" t="n">
-        <v>6848356</v>
+        <v>6848274</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,12 +1737,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,60 +1762,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128937356</v>
+        <v>128938096</v>
       </c>
       <c r="B13" t="n">
-        <v>97595</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476538</v>
+        <v>476310</v>
       </c>
       <c r="R13" t="n">
-        <v>6848401</v>
+        <v>6848364</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,6 +1854,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Små plantor i tidig fas.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,22 +1873,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128938294</v>
+        <v>128938254</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1938,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476273</v>
+        <v>476311</v>
       </c>
       <c r="R14" t="n">
-        <v>6848367</v>
+        <v>6848373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128940838</v>
+        <v>128938294</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,26 +2010,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476019</v>
+        <v>476273</v>
       </c>
       <c r="R15" t="n">
-        <v>6848346</v>
+        <v>6848367</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,45 +2079,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128940807</v>
+        <v>128938430</v>
       </c>
       <c r="B16" t="n">
-        <v>97601</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476017</v>
+        <v>476242</v>
       </c>
       <c r="R16" t="n">
-        <v>6848311</v>
+        <v>6848360</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2203,45 +2185,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128939810</v>
+        <v>128938481</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476160</v>
+        <v>476239</v>
       </c>
       <c r="R17" t="n">
-        <v>6848351</v>
+        <v>6848323</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,7 +2294,7 @@
         <v>128938486</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941680</v>
+        <v>128939967</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,29 +2425,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476579</v>
+        <v>476108</v>
       </c>
       <c r="R19" t="n">
-        <v>6848505</v>
+        <v>6848326</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2500,22 +2482,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128939967</v>
+        <v>128940018</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,20 +2522,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476108</v>
+        <v>476093</v>
       </c>
       <c r="R20" t="n">
-        <v>6848326</v>
+        <v>6848323</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,57 +2588,66 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128939377</v>
+        <v>128940061</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476172</v>
+        <v>476098</v>
       </c>
       <c r="R21" t="n">
-        <v>6848367</v>
+        <v>6848356</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128939975</v>
+        <v>128940754</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476095</v>
+        <v>475993</v>
       </c>
       <c r="R22" t="n">
-        <v>6848329</v>
+        <v>6848330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,45 +2803,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128940964</v>
+        <v>128940813</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476162</v>
+        <v>476011</v>
       </c>
       <c r="R23" t="n">
-        <v>6848440</v>
+        <v>6848344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,22 +2897,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128938481</v>
+        <v>128940838</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2939,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2944,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476239</v>
+        <v>476019</v>
       </c>
       <c r="R24" t="n">
-        <v>6848323</v>
+        <v>6848346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,10 +3015,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128940018</v>
+        <v>128940871</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3045,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3050,10 +3059,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476093</v>
+        <v>476032</v>
       </c>
       <c r="R25" t="n">
-        <v>6848323</v>
+        <v>6848339</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,10 +3121,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128940754</v>
+        <v>128941680</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,17 +3149,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475993</v>
+        <v>476579</v>
       </c>
       <c r="R26" t="n">
-        <v>6848330</v>
+        <v>6848505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,10 +3227,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128940871</v>
+        <v>128941699</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,29 +3255,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476032</v>
+        <v>476591</v>
       </c>
       <c r="R27" t="n">
-        <v>6848339</v>
+        <v>6848497</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3303,22 +3312,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128941699</v>
+        <v>128941818</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,17 +3355,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476591</v>
+        <v>476588</v>
       </c>
       <c r="R28" t="n">
-        <v>6848497</v>
+        <v>6848599</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3400,22 +3409,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128941818</v>
+        <v>128941893</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3440,20 +3449,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476588</v>
+        <v>476608</v>
       </c>
       <c r="R29" t="n">
-        <v>6848599</v>
+        <v>6848604</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3509,10 +3527,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128938096</v>
+        <v>128941972</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,7 +3557,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3549,14 +3567,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476310</v>
+        <v>476631</v>
       </c>
       <c r="R30" t="n">
-        <v>6848364</v>
+        <v>6848589</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3591,11 +3609,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Små plantor i tidig fas.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3608,69 +3621,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128941972</v>
+        <v>128940807</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>97989</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Örnsjöheden, Örnsjöheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476631</v>
+        <v>476017</v>
       </c>
       <c r="R31" t="n">
-        <v>6848589</v>
+        <v>6848311</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3723,6 +3727,103 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128937356</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>476538</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6848401</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128939377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128939810</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128939975</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940090</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940964</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938038</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128939797</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124080304</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825368</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825371</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1882,6 +1942,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938096</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1979,6 +2044,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938254</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2076,6 +2146,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938294</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938430</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938481</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938486</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2491,6 +2581,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128939967</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940018</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2703,6 +2803,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940061</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2800,6 +2905,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940754</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940813</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3012,6 +3127,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940838</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3118,6 +3238,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940871</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3224,6 +3349,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128941680</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3321,6 +3451,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128941699</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3418,6 +3553,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128941818</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3524,6 +3664,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128941893</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,6 +3775,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128941972</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3727,6 +3877,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940807</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3824,8 +3979,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128937356</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>